--- a/analysis/statistics/All_Statistics.xlsx
+++ b/analysis/statistics/All_Statistics.xlsx
@@ -20,13 +20,19 @@
     <sheet name="Table_2_Keyboard" sheetId="12" r:id="rId14"/>
     <sheet name="Table_2_Reaching" sheetId="13" r:id="rId15"/>
     <sheet name="Prime_Obj_Aware" sheetId="14" r:id="rId16"/>
+    <sheet name="Tree1_Congruency_Flavor1" sheetId="15" r:id="rId17"/>
+    <sheet name="TreeS1_PreReg_Original" sheetId="16" r:id="rId18"/>
+    <sheet name="TreeS2_Standardized" sheetId="17" r:id="rId19"/>
+    <sheet name="Tree2_Relative_Sensitivity" sheetId="18" r:id="rId20"/>
+    <sheet name="Chrono_Traj_Clusters" sheetId="19" r:id="rId21"/>
+    <sheet name="Chrono_Sensitivity_Contrasts" sheetId="20" r:id="rId22"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1336" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1512" uniqueCount="474">
   <si>
     <t>name</t>
   </si>
@@ -1271,6 +1277,183 @@
   </si>
   <si>
     <t>reach_CI_high</t>
+  </si>
+  <si>
+    <t>Node_Name</t>
+  </si>
+  <si>
+    <t>Manuscript</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Reaching</t>
+  </si>
+  <si>
+    <t>Confirmatory_KB</t>
+  </si>
+  <si>
+    <t>Keyboard_RT</t>
+  </si>
+  <si>
+    <t>PR_Confirmatory_Reach</t>
+  </si>
+  <si>
+    <t>Reach_Area</t>
+  </si>
+  <si>
+    <t>PR_Exploratory_Reach</t>
+  </si>
+  <si>
+    <t>Reaching_Onset</t>
+  </si>
+  <si>
+    <t>Reaching_Duration_MT</t>
+  </si>
+  <si>
+    <t>Total_Distance</t>
+  </si>
+  <si>
+    <t>Changes_of_Mind_COM</t>
+  </si>
+  <si>
+    <t>Spatial_Deviation_Cluster</t>
+  </si>
+  <si>
+    <t>Spatial_Variation_Cluster</t>
+  </si>
+  <si>
+    <t>PostHoc_Exploratory_Reach</t>
+  </si>
+  <si>
+    <t>MAD</t>
+  </si>
+  <si>
+    <t>AUC</t>
+  </si>
+  <si>
+    <t>Implied_End_Point_Cluster</t>
+  </si>
+  <si>
+    <t>Node_Type</t>
+  </si>
+  <si>
+    <t>Internal_Family</t>
+  </si>
+  <si>
+    <t>PreReg_Leaf</t>
+  </si>
+  <si>
+    <t>PostHoc_Leaf</t>
+  </si>
+  <si>
+    <t>Uncorrected_p</t>
+  </si>
+  <si>
+    <t>TreeBH_FDR_q</t>
+  </si>
+  <si>
+    <t>Significant_FDR</t>
+  </si>
+  <si>
+    <t>Heading_Angle_Cluster_1</t>
+  </si>
+  <si>
+    <t>Heading_Angle_Cluster_2</t>
+  </si>
+  <si>
+    <t>Sensitivity_Advantage</t>
+  </si>
+  <si>
+    <t>Confirmatory_Comparison</t>
+  </si>
+  <si>
+    <t>Exploratory_Comparisons</t>
+  </si>
+  <si>
+    <t>Diff_Reach_Area_vs_KB</t>
+  </si>
+  <si>
+    <t>PR_Exploratory_Diffs</t>
+  </si>
+  <si>
+    <t>Diff_MT_vs_KB</t>
+  </si>
+  <si>
+    <t>Diff_Total_Dist_vs_KB</t>
+  </si>
+  <si>
+    <t>Diff_Onset_vs_KB</t>
+  </si>
+  <si>
+    <t>Diff_COM_vs_KB</t>
+  </si>
+  <si>
+    <t>Diff_Spatial_Dev_vs_KB</t>
+  </si>
+  <si>
+    <t>Diff_Spatial_Var_vs_KB</t>
+  </si>
+  <si>
+    <t>PostHoc_Exploratory_Diffs</t>
+  </si>
+  <si>
+    <t>Diff_MAD_vs_KB</t>
+  </si>
+  <si>
+    <t>Diff_AUC_vs_KB</t>
+  </si>
+  <si>
+    <t>Diff_IEP_vs_KB</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Deviation_From_Center</t>
+  </si>
+  <si>
+    <t>Implied_End_Point</t>
+  </si>
+  <si>
+    <t>Heading_Angle</t>
+  </si>
+  <si>
+    <t>Movement_Variation</t>
+  </si>
+  <si>
+    <t>Cluster_Detected</t>
+  </si>
+  <si>
+    <t>Start_Sample</t>
+  </si>
+  <si>
+    <t>End_Sample</t>
+  </si>
+  <si>
+    <t>Cluster_p_raw</t>
+  </si>
+  <si>
+    <t>FDR_adj_p</t>
+  </si>
+  <si>
+    <t>Contrast</t>
+  </si>
+  <si>
+    <t>Peak_Deviation_vs_KB</t>
+  </si>
+  <si>
+    <t>Peak_IEP_vs_KB</t>
+  </si>
+  <si>
+    <t>Peak_Heading_Angle_vs_KB</t>
+  </si>
+  <si>
+    <t>Delta_dz</t>
+  </si>
+  <si>
+    <t>Raw_p_TwoSided</t>
   </si>
 </sst>
 </file>
@@ -5942,6 +6125,1370 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.21875" customWidth="true"/>
+    <col min="2" max="2" width="13.5546875" customWidth="true"/>
+    <col min="3" max="3" width="14.5546875" customWidth="true"/>
+    <col min="4" max="4" width="14.5546875" customWidth="true"/>
+    <col min="5" max="5" width="13.5546875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C2" s="0"/>
+      <c r="D2" s="0">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C4" s="0"/>
+      <c r="D4" s="0">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="E7" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="E8" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.038300000000000001</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0.038300000000000001</v>
+      </c>
+      <c r="E10" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.017100000000000001</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0.025649999999999999</v>
+      </c>
+      <c r="E13" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.0042473037157992888</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0.0084946074315985776</v>
+      </c>
+      <c r="E14" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0.028306976867669587</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0.033968372241203505</v>
+      </c>
+      <c r="E15" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="E16" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0.00020000000000000001</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0.00060000000000000006</v>
+      </c>
+      <c r="E17" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0.00050000000000000001</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0.00075000000000000002</v>
+      </c>
+      <c r="E18" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="C19" s="0">
+        <v>0.00081508568493560141</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0.00081508568493560141</v>
+      </c>
+      <c r="E19" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.88671875" customWidth="true"/>
+    <col min="2" max="2" width="13.5546875" customWidth="true"/>
+    <col min="3" max="3" width="15.5546875" customWidth="true"/>
+    <col min="4" max="4" width="14.5546875" customWidth="true"/>
+    <col min="5" max="5" width="13.5546875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C2" s="0"/>
+      <c r="D2" s="0">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C4" s="0"/>
+      <c r="D4" s="0">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="E7" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="E8" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.038300000000000001</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0.043771428571428572</v>
+      </c>
+      <c r="E10" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.017100000000000001</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0.027360000000000002</v>
+      </c>
+      <c r="E13" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.0042473037157992888</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0.0084946074315985776</v>
+      </c>
+      <c r="E14" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0.028306976867669587</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0.037742635823559447</v>
+      </c>
+      <c r="E15" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C16" s="0">
+        <v>0.00067890358541489171</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0.0018104095611063777</v>
+      </c>
+      <c r="E16" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0.045993414863170545</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0.045993414863170545</v>
+      </c>
+      <c r="E17" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.21875" customWidth="true"/>
+    <col min="2" max="2" width="13.5546875" customWidth="true"/>
+    <col min="3" max="3" width="14.5546875" customWidth="true"/>
+    <col min="4" max="4" width="13.5546875" customWidth="true"/>
+    <col min="5" max="5" width="13.5546875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C2" s="0"/>
+      <c r="D2" s="0">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C4" s="0"/>
+      <c r="D4" s="0">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="E7" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.00080000000000000004</v>
+      </c>
+      <c r="E8" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.042999999999999997</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0.042999999999999997</v>
+      </c>
+      <c r="E10" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.017100000000000001</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0.025649999999999999</v>
+      </c>
+      <c r="E13" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.0065829962270091968</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0.013165992454018394</v>
+      </c>
+      <c r="E14" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0.022505535322203229</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0.027006642386643874</v>
+      </c>
+      <c r="E15" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0.00050000000000000001</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0.00050000000000000001</v>
+      </c>
+      <c r="E18" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="C19" s="0">
+        <v>0.00029688408186856474</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0.00044532612280284711</v>
+      </c>
+      <c r="E19" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="true"/>
+    <col min="2" max="2" width="13.5546875" customWidth="true"/>
+    <col min="3" max="3" width="13.21875" customWidth="true"/>
+    <col min="4" max="4" width="13.21875" customWidth="true"/>
+    <col min="5" max="5" width="13.5546875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C2" s="0"/>
+      <c r="D2" s="0">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E2" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C3" s="0"/>
+      <c r="D3" s="0">
+        <v>0.095600000000000004</v>
+      </c>
+      <c r="E3" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C4" s="0"/>
+      <c r="D4" s="0">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="E4" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.095600000000000004</v>
+      </c>
+      <c r="D5" s="0">
+        <v>0.095600000000000004</v>
+      </c>
+      <c r="E5" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C6" s="0"/>
+      <c r="D6" s="0">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="E6" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.98040000000000005</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0.98040000000000005</v>
+      </c>
+      <c r="E7" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.53939999999999999</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.64727999999999997</v>
+      </c>
+      <c r="E8" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.0080000000000000002</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0.016</v>
+      </c>
+      <c r="E9" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.0016000000000000001</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0.0090000000000000011</v>
+      </c>
+      <c r="E10" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0.050799999999999998</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0.07619999999999999</v>
+      </c>
+      <c r="E11" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.0030000000000000001</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0.0090000000000000011</v>
+      </c>
+      <c r="E12" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0">
+        <v>0.19019999999999998</v>
+      </c>
+      <c r="E13" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="E14" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0.1268</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0.19019999999999998</v>
+      </c>
+      <c r="E15" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="C16" s="0">
+        <v>0.075200000000000003</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0.19019999999999998</v>
+      </c>
+      <c r="E16" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.44140625" customWidth="true"/>
+    <col min="2" max="2" width="15.109375" customWidth="true"/>
+    <col min="3" max="3" width="11.77734375" customWidth="true"/>
+    <col min="4" max="4" width="10.88671875" customWidth="true"/>
+    <col min="5" max="5" width="12.5546875" customWidth="true"/>
+    <col min="6" max="6" width="14.5546875" customWidth="true"/>
+    <col min="7" max="7" width="14.5546875" customWidth="true"/>
+    <col min="8" max="8" width="13.5546875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>466</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0">
+        <v>19</v>
+      </c>
+      <c r="D2" s="0">
+        <v>34</v>
+      </c>
+      <c r="E2" s="0">
+        <v>0.71521349767835019</v>
+      </c>
+      <c r="F2" s="0">
+        <v>0.029502084943594964</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0.039336113258126616</v>
+      </c>
+      <c r="H2" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="B3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" s="0">
+        <v>34</v>
+      </c>
+      <c r="E3" s="0">
+        <v>0.71402566621136665</v>
+      </c>
+      <c r="F3" s="0">
+        <v>0.002547037964738097</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.0075025174760470215</v>
+      </c>
+      <c r="H3" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0">
+        <v>15</v>
+      </c>
+      <c r="D4" s="0">
+        <v>31</v>
+      </c>
+      <c r="E4" s="0">
+        <v>0.64672994369148595</v>
+      </c>
+      <c r="F4" s="0">
+        <v>0.0037512587380235107</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.0075025174760470215</v>
+      </c>
+      <c r="H4" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>462</v>
+      </c>
+      <c r="B5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0">
+        <v>1</v>
+      </c>
+      <c r="H5" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N14"/>
@@ -6577,6 +8124,116 @@
       </c>
       <c r="N14" s="0">
         <v>0.59396884390521521</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.44140625" customWidth="true"/>
+    <col min="2" max="2" width="12.5546875" customWidth="true"/>
+    <col min="3" max="3" width="14.21875" customWidth="true"/>
+    <col min="4" max="4" width="11.5546875" customWidth="true"/>
+    <col min="5" max="5" width="15.44140625" customWidth="true"/>
+    <col min="6" max="6" width="9.6640625" customWidth="true"/>
+    <col min="7" max="7" width="13.5546875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B2" s="0">
+        <v>0.45824496371123225</v>
+      </c>
+      <c r="C2" s="0">
+        <v>-0.060029566180442195</v>
+      </c>
+      <c r="D2" s="0">
+        <v>1.0369648377906495</v>
+      </c>
+      <c r="E2" s="0">
+        <v>0.074999999999999997</v>
+      </c>
+      <c r="F2" s="0">
+        <v>0.074999999999999997</v>
+      </c>
+      <c r="G2" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="B3" s="0">
+        <v>0.45943279517821578</v>
+      </c>
+      <c r="C3" s="0">
+        <v>-0.030243245797282936</v>
+      </c>
+      <c r="D3" s="0">
+        <v>1.0452770349562317</v>
+      </c>
+      <c r="E3" s="0">
+        <v>0.065799999999999997</v>
+      </c>
+      <c r="F3" s="0">
+        <v>0.074999999999999997</v>
+      </c>
+      <c r="G3" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="B4" s="0">
+        <v>0.52672851769809648</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.05209931664243822</v>
+      </c>
+      <c r="D4" s="0">
+        <v>1.1087759293411996</v>
+      </c>
+      <c r="E4" s="0">
+        <v>0.030200000000000001</v>
+      </c>
+      <c r="F4" s="0">
+        <v>0.074999999999999997</v>
+      </c>
+      <c r="G4" s="0" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7430,7 +9087,7 @@
         <v>4.634766725884397</v>
       </c>
       <c r="J6" s="0">
-        <v>0</v>
+        <v>0.0084946074315985776</v>
       </c>
     </row>
     <row r="7">
@@ -7462,7 +9119,7 @@
         <v>7.048888581322224</v>
       </c>
       <c r="J7" s="0">
-        <v>0</v>
+        <v>0.00081508568493560141</v>
       </c>
     </row>
     <row r="8">
@@ -7558,7 +9215,7 @@
         <v>3.5556465049270245</v>
       </c>
       <c r="J10" s="0">
-        <v>0</v>
+        <v>0.033968372241203505</v>
       </c>
     </row>
     <row r="11">
@@ -17644,7 +19301,7 @@
         <v>16.983272561609933</v>
       </c>
       <c r="S2" s="0">
-        <v>4.9673610577245915e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -17821,7 +19478,7 @@
         <v>0.0090481438540074687</v>
       </c>
       <c r="S5" s="0">
-        <v>0.00012447884143922553</v>
+        <v>0.00060000000000000006</v>
       </c>
     </row>
     <row r="6">
